--- a/data/trans_camb/IP1005-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Habitat-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,37</t>
+          <t>-0,79; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,39</t>
+          <t>-0,79; 1,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,17</t>
+          <t>-0,39; 1,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,73</t>
+          <t>-0,42; 0,96</t>
         </is>
       </c>
     </row>
@@ -792,27 +792,27 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,99</t>
+          <t>-0,43; 1,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,95</t>
+          <t>-0,35; 2,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,32</t>
+          <t>-0,81; 0,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,44</t>
+          <t>-0,17; 1,55</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,29</t>
+          <t>-2,59; 0,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,43</t>
+          <t>-2,54; 0,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,14</t>
+          <t>-1,37; 0,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,86</t>
+          <t>-0,91; 0,81</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,66</t>
+          <t>-1,02; 0,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,0</t>
+          <t>-2,02; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,0</t>
+          <t>-0,84; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,39</t>
+          <t>-0,51; 0,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,5</t>
+          <t>-0,41; 0,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,27</t>
+          <t>-0,47; 0,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,88</t>
+          <t>-0,22; 0,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,23</t>
+          <t>-0,39; 0,18</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,51</t>
+          <t>-0,19; 0,49</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-89,34; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-68,2; —</t>
+          <t>-73,1; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,3; 236,25</t>
+          <t>-83,34; 171,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-48,43; 407,83</t>
+          <t>-47,05; 370,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1005-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Habitat-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,35</t>
+          <t>-0,38; 1,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,96</t>
+          <t>-0,41; 0,76</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,88</t>
+          <t>-0,44; 2,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,17 +802,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,2</t>
+          <t>-0,33; 2,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,33</t>
+          <t>-0,81; 0,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,55</t>
+          <t>-0,19; 1,52</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-78,28; —</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,29</t>
+          <t>-2,99; 0,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 0,31</t>
+          <t>-2,84; 0,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,17</t>
+          <t>-1,27; 0,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,81</t>
+          <t>-0,98; 0,78</t>
         </is>
       </c>
     </row>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,0</t>
+          <t>-2,03; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,32</t>
+          <t>-0,52; 0,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,0</t>
+          <t>-0,95; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,38</t>
+          <t>-0,5; 0,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,51</t>
+          <t>-0,41; 0,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,28</t>
+          <t>-0,48; 0,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,83</t>
+          <t>-0,22; 0,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,18</t>
+          <t>-0,38; 0,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,49</t>
+          <t>-0,22; 0,48</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-73,1; —</t>
+          <t>-73,89; 1195,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 171,45</t>
+          <t>-83,73; 231,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 370,12</t>
+          <t>-56,44; 340,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1005-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1005-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,05</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>-1,12; 1,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,79; 1,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,35</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,18</t>
+          <t>-0,21; 1,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,76</t>
+          <t>-0,42; 0,73</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16,17%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,72%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,62</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,56</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>-1,29; 0,0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>-0,37; 1,95</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>-0,66; 1,02</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,44; 2,07</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,6; 0,0</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,13</t>
+          <t>-0,43; 1,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,32</t>
+          <t>-0,82; 0,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,52</t>
+          <t>-0,24; 1,44</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>192,29%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>169,98%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>192,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,28; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,64</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,31</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,85; 0,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>-2,61; 0,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,14</t>
+          <t>-1,57; 0,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,78</t>
+          <t>-0,96; 0,86</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-69,82%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-67,61%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,35; 0,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,68; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,48</t>
+          <t>-0,51; 0,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,0</t>
+          <t>-0,93; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-3,77%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-3,77%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,04</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,37</t>
+          <t>-0,56; 0,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,55</t>
+          <t>-0,22; 0,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,27</t>
+          <t>-0,48; 0,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,82</t>
+          <t>-0,42; 0,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,22</t>
+          <t>-0,35; 0,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,48</t>
+          <t>-0,19; 0,51</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-34,16%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-11,12%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>15,1%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-34,16%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>89,61%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-68,2; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-73,89; 1195,53</t>
+          <t>-89,34; —</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-83,73; 231,72</t>
+          <t>-83,3; 236,25</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 340,48</t>
+          <t>-48,43; 407,83</t>
         </is>
       </c>
     </row>
